--- a/GWD Data/Well Protection.xlsx
+++ b/GWD Data/Well Protection.xlsx
@@ -294,8 +294,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEAD1DC"/>
-        <bgColor rgb="FFEAD1DC"/>
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>

--- a/GWD Data/Well Protection.xlsx
+++ b/GWD Data/Well Protection.xlsx
@@ -1,17 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView xWindow="240" yWindow="120" windowWidth="14940" windowHeight="9225" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Well Protection" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="36">
   <si>
     <t>Well Protection Cover</t>
   </si>
@@ -63,18 +67,20 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Merriweather"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <sz val="12.0"/>
+        <rFont val="Cambria"/>
+        <family val="2"/>
       </rPr>
       <t>m</t>
     </r>
     <r>
       <rPr>
-        <rFont val="Merriweather"/>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <sz val="12.0"/>
-        <vertAlign val="superscript"/>
+        <rFont val="Cambria"/>
+        <family val="2"/>
       </rPr>
       <t>3</t>
     </r>
@@ -86,122 +92,48 @@
     <t xml:space="preserve"> Side Wall</t>
   </si>
   <si>
+    <t>Providing and laying in position specified grade of reinforced cement concrete, excluding the cost of centering, shuttering, finishing and reinforcement - All work up to plinth level: 1:2:4 as per DSR item 5.1.3</t>
+  </si>
+  <si>
+    <t>Slab</t>
+  </si>
+  <si>
+    <t>Steel reinforcement for R.C.C. work including straightening, cutting, bending, placing in position and binding all complete above plinth level (Mild and Medium Tensile steel bars) as per DSR item 5.22.1</t>
+  </si>
+  <si>
+    <t>Quantity as item 4</t>
+  </si>
+  <si>
+    <t>at  80 kg/m3</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>Centering and shuttering including strutting, propping etc. and removal of form for roofs etc. for mass concrete as per DSR item 5.9.3</t>
+  </si>
+  <si>
     <r>
       <rPr>
-        <rFont val="Merriweather"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <sz val="12.0"/>
+        <rFont val="Cambria"/>
+        <family val="2"/>
       </rPr>
       <t>m</t>
     </r>
     <r>
       <rPr>
-        <rFont val="Merriweather"/>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <sz val="12.0"/>
-        <vertAlign val="superscript"/>
-      </rPr>
-      <t>3</t>
-    </r>
-  </si>
-  <si>
-    <t>Providing and laying in position specified grade of reinforced cement concrete, excluding the cost of centering, shuttering, finishing and reinforcement - All work up to plinth level: 1:2:4 as per DSR item 5.1.3</t>
-  </si>
-  <si>
-    <t>Slab</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Merriweather"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t>m</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Merriweather"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-        <vertAlign val="superscript"/>
-      </rPr>
-      <t>3</t>
-    </r>
-  </si>
-  <si>
-    <t>Steel reinforcement for R.C.C. work including straightening, cutting, bending, placing in position and binding all complete above plinth level (Mild and Medium Tensile steel bars) as per DSR item 5.22.1</t>
-  </si>
-  <si>
-    <t>Quantity as item 4</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Merriweather"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t>m</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Merriweather"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-        <vertAlign val="superscript"/>
-      </rPr>
-      <t>3</t>
-    </r>
-  </si>
-  <si>
-    <t>at  80 kg/m3</t>
-  </si>
-  <si>
-    <t>kg</t>
-  </si>
-  <si>
-    <t>Centering and shuttering including strutting, propping etc. and removal of form for roofs etc. for mass concrete as per DSR item 5.9.3</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Merriweather"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t>m</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Merriweather"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-        <vertAlign val="superscript"/>
+        <rFont val="Cambria"/>
+        <family val="2"/>
       </rPr>
       <t>2</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Merriweather"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t>m</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Merriweather"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-        <vertAlign val="superscript"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
     <t>12 mm cement plaster of mix 1:4 as per DSR item  13.1.1</t>
   </si>
   <si>
@@ -218,25 +150,6 @@
   </si>
   <si>
     <t>Side of slab</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Merriweather"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t>m</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Merriweather"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-        <vertAlign val="superscript"/>
-      </rPr>
-      <t>2</t>
-    </r>
   </si>
   <si>
     <t>Unforeseen if any</t>
@@ -251,38 +164,54 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="6">
-    <numFmt numFmtId="164" formatCode="0.00;[RED]0.00"/>
-    <numFmt numFmtId="165" formatCode="0.0000;[RED]0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.0000;[RED]\-0.0000"/>
-    <numFmt numFmtId="167" formatCode="0.000;[RED]0.000"/>
-    <numFmt numFmtId="168" formatCode="0.000;[RED]\-0.000"/>
-    <numFmt numFmtId="169" formatCode="0.000"/>
+    <numFmt numFmtId="177" formatCode="0.000"/>
+    <numFmt numFmtId="178" formatCode="0.000;[RED]\-0.000"/>
+    <numFmt numFmtId="179" formatCode="0.000;[RED]0.000"/>
+    <numFmt numFmtId="180" formatCode="0.0000;[RED]\-0.0000"/>
+    <numFmt numFmtId="181" formatCode="0.0000;[RED]0.0000"/>
+    <numFmt numFmtId="182" formatCode="0.00;[RED]0.00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Cambria"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Cambria"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Cambria"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12.0"/>
+      <vertAlign val="superscript"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Merriweather"/>
-    </font>
-    <font>
-      <sz val="12.0"/>
-      <color theme="1"/>
-      <name val="Merriweather"/>
-    </font>
-    <font/>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
+      <name val="Cambria"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -290,17 +219,23 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="5">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF3D3D3D"/>
@@ -319,6 +254,7 @@
       <left style="thin">
         <color rgb="FF3D3D3D"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF3D3D3D"/>
       </top>
@@ -327,6 +263,8 @@
       </bottom>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF3D3D3D"/>
       </top>
@@ -335,6 +273,7 @@
       </bottom>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF3D3D3D"/>
       </right>
@@ -346,133 +285,314 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+  <cellXfs count="19">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="15" builtinId="5"/>
+    <cellStyle name="Currency" xfId="16" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
+    <cellStyle name="Comma" xfId="18" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Sheets">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="000000"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285F4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EA4335"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="FBBC04"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34A853"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="FF6D01"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46BDC6"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Sheets">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -613,34 +733,27 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <tabColor rgb="FFFF00FF"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="4.0"/>
-    <col customWidth="1" min="2" max="2" width="18.5"/>
-    <col customWidth="1" min="3" max="3" width="4.13"/>
-    <col customWidth="1" min="4" max="5" width="5.0"/>
-    <col customWidth="1" min="6" max="6" width="6.38"/>
-    <col customWidth="1" min="7" max="7" width="10.38"/>
-    <col customWidth="1" min="8" max="8" width="5.13"/>
-    <col customWidth="1" min="9" max="9" width="8.38"/>
-    <col customWidth="1" min="10" max="10" width="9.0"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C74E1D98-5427-460A-B369-D3898F98B9A6}">
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1" ht="12.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" ht="12.75">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -672,9 +785,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10" ht="12.75">
       <c r="A3" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>11</v>
@@ -688,13 +801,13 @@
       <c r="I3" s="6"/>
       <c r="J3" s="7"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10" ht="12.75">
       <c r="A4" s="2"/>
       <c r="B4" s="8" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2">
         <v>0.75</v>
@@ -703,7 +816,7 @@
         <v>0.75</v>
       </c>
       <c r="F4" s="2">
-        <v>0.2</v>
+        <v>0.20</v>
       </c>
       <c r="G4" s="9">
         <f>PRODUCT(C4:F4)</f>
@@ -713,7 +826,7 @@
       <c r="I4" s="2"/>
       <c r="J4" s="4"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:10" ht="12.75">
       <c r="A5" s="2"/>
       <c r="B5" s="8" t="s">
         <v>7</v>
@@ -726,22 +839,22 @@
         <f>SUM(G4)</f>
         <v>0.1125</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="2">
         <v>249.03</v>
       </c>
       <c r="J5" s="4">
         <f>G5*I5</f>
-        <v>28.015875</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>28.015875000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="12.75">
       <c r="A6" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="B6" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>14</v>
       </c>
       <c r="C6" s="6"/>
@@ -753,13 +866,13 @@
       <c r="I6" s="6"/>
       <c r="J6" s="7"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:10" ht="12.75">
       <c r="A7" s="2"/>
       <c r="B7" s="8" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="2">
         <v>0.75</v>
@@ -768,42 +881,42 @@
         <v>0.75</v>
       </c>
       <c r="F7" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="G7" s="13">
-        <f t="shared" ref="G7:G8" si="1">PRODUCT(C7:F7)</f>
+        <v>0.10</v>
+      </c>
+      <c r="G7" s="12">
+        <f>PRODUCT(C7:F7)</f>
         <v>0.05625</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="4"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:10" ht="12.75">
       <c r="A8" s="2"/>
       <c r="B8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="2">
         <v>3.14</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="2">
         <v>0.07</v>
       </c>
       <c r="E8" s="2">
         <v>0.07</v>
       </c>
-      <c r="F8" s="11">
-        <v>0.1</v>
-      </c>
-      <c r="G8" s="13">
-        <f t="shared" si="1"/>
+      <c r="F8" s="2">
+        <v>0.10</v>
+      </c>
+      <c r="G8" s="12">
+        <f>PRODUCT(C8:F8)</f>
         <v>0.0015386</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="4"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:10" ht="12.75">
       <c r="A9" s="2"/>
       <c r="B9" s="8" t="s">
         <v>7</v>
@@ -812,14 +925,14 @@
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
-      <c r="G9" s="13">
+      <c r="G9" s="12">
         <f>G7-G8</f>
         <v>0.0547114</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="2">
         <v>5491.79</v>
       </c>
       <c r="J9" s="4">
@@ -827,11 +940,11 @@
         <v>300.4635194</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:10" ht="12.75">
       <c r="A10" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="B10" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="6"/>
@@ -843,24 +956,24 @@
       <c r="I10" s="6"/>
       <c r="J10" s="7"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:10" ht="12.75">
       <c r="A11" s="2"/>
       <c r="B11" s="8" t="s">
         <v>18</v>
       </c>
       <c r="C11" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D11" s="2">
         <v>0.65</v>
       </c>
       <c r="E11" s="2">
-        <v>0.1</v>
+        <v>0.10</v>
       </c>
       <c r="F11" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="G11" s="13">
+        <v>0.60</v>
+      </c>
+      <c r="G11" s="12">
         <f>PRODUCT(C11:F11)</f>
         <v>0.156</v>
       </c>
@@ -868,7 +981,7 @@
       <c r="I11" s="2"/>
       <c r="J11" s="4"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:10" ht="12.75">
       <c r="A12" s="2"/>
       <c r="B12" s="8" t="s">
         <v>7</v>
@@ -877,14 +990,14 @@
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
-      <c r="G12" s="14">
+      <c r="G12" s="13">
         <f>SUM(G11)</f>
         <v>0.156</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I12" s="11">
+        <v>16</v>
+      </c>
+      <c r="I12" s="2">
         <v>7195.35</v>
       </c>
       <c r="J12" s="4">
@@ -892,12 +1005,12 @@
         <v>1122.4746</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:10" ht="12.75">
       <c r="A13" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>20</v>
+        <v>4</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>19</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -908,32 +1021,32 @@
       <c r="I13" s="6"/>
       <c r="J13" s="7"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:10" ht="12.75">
       <c r="A14" s="2"/>
       <c r="B14" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C14" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="2">
-        <v>0.8</v>
+        <v>0.80</v>
       </c>
       <c r="E14" s="2">
-        <v>0.8</v>
+        <v>0.80</v>
       </c>
       <c r="F14" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="G14" s="13">
+        <v>0.10</v>
+      </c>
+      <c r="G14" s="12">
         <f>PRODUCT(C14:F14)</f>
-        <v>0.064</v>
+        <v>0.064000000000000001</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="4"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:10" ht="12.75">
       <c r="A15" s="2"/>
       <c r="B15" s="8" t="s">
         <v>7</v>
@@ -942,27 +1055,27 @@
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
-      <c r="G15" s="14">
+      <c r="G15" s="13">
         <f>SUM(G14)</f>
-        <v>0.064</v>
+        <v>0.064000000000000001</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I15" s="11">
+        <v>16</v>
+      </c>
+      <c r="I15" s="2">
         <v>6897.84</v>
       </c>
       <c r="J15" s="4">
         <f>G15*I15</f>
-        <v>441.46176</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>441.46176000000003</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="12.75">
       <c r="A16" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>23</v>
+        <v>5</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
@@ -973,47 +1086,47 @@
       <c r="I16" s="6"/>
       <c r="J16" s="7"/>
     </row>
-    <row r="17">
+    <row r="17" spans="1:10" ht="12.75">
       <c r="A17" s="2"/>
       <c r="B17" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
-      <c r="G17" s="13">
+      <c r="G17" s="12">
         <f>G15</f>
-        <v>0.064</v>
+        <v>0.064000000000000001</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="4"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:10" ht="12.75">
       <c r="A18" s="2"/>
       <c r="B18" s="8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2">
-        <v>80.0</v>
-      </c>
-      <c r="F18" s="15">
+        <v>80</v>
+      </c>
+      <c r="F18" s="14">
         <f>G17</f>
-        <v>0.064</v>
-      </c>
-      <c r="G18" s="13">
+        <v>0.064000000000000001</v>
+      </c>
+      <c r="G18" s="12">
         <f>PRODUCT(C18:F18)</f>
         <v>5.12</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I18" s="11">
+        <v>24</v>
+      </c>
+      <c r="I18" s="2">
         <v>77.22</v>
       </c>
       <c r="J18" s="4">
@@ -1021,12 +1134,12 @@
         <v>395.3664</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:10" ht="12.75">
       <c r="A19" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>28</v>
+        <v>6</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
@@ -1037,34 +1150,34 @@
       <c r="I19" s="6"/>
       <c r="J19" s="7"/>
     </row>
-    <row r="20">
+    <row r="20" spans="1:10" ht="12.75">
       <c r="A20" s="2"/>
       <c r="B20" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="11">
-        <v>4.0</v>
+        <v>20</v>
+      </c>
+      <c r="C20" s="2">
+        <v>4</v>
       </c>
       <c r="D20" s="2">
         <f>D14</f>
-        <v>0.8</v>
+        <v>0.80</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2">
         <f>F14</f>
-        <v>0.1</v>
-      </c>
-      <c r="G20" s="13">
+        <v>0.10</v>
+      </c>
+      <c r="G20" s="12">
         <f>PRODUCT(C20:F20)</f>
         <v>0.32</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="4"/>
     </row>
-    <row r="21">
+    <row r="21" spans="1:10" ht="12.75">
       <c r="A21" s="2"/>
       <c r="B21" s="8" t="s">
         <v>7</v>
@@ -1073,27 +1186,27 @@
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
-      <c r="G21" s="13">
+      <c r="G21" s="12">
         <f>SUM(G20)</f>
         <v>0.32</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I21" s="11">
+        <v>26</v>
+      </c>
+      <c r="I21" s="2">
         <v>665.45</v>
       </c>
       <c r="J21" s="4">
         <f>G21*I21</f>
-        <v>212.944</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>212.94399999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="12.75">
       <c r="A22" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>31</v>
+        <v>7</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
@@ -1104,36 +1217,36 @@
       <c r="I22" s="6"/>
       <c r="J22" s="7"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:10" ht="12.75">
       <c r="A23" s="2"/>
       <c r="B23" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C23" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="D23" s="11">
+        <v>4</v>
+      </c>
+      <c r="D23" s="2">
         <v>0.75</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="G23" s="13">
-        <f t="shared" ref="G23:G24" si="2">PRODUCT(C23:F23)</f>
-        <v>1.5</v>
+        <v>0.50</v>
+      </c>
+      <c r="G23" s="12">
+        <f>PRODUCT(C23:F23)</f>
+        <v>1.50</v>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="4"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:10" ht="12.75">
       <c r="A24" s="2"/>
       <c r="B24" s="8" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C24" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D24" s="2">
         <f>D23-2*E11</f>
@@ -1141,33 +1254,33 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="G24" s="13">
-        <f t="shared" si="2"/>
+        <v>0.60</v>
+      </c>
+      <c r="G24" s="12">
+        <f>PRODUCT(C24:F24)</f>
         <v>1.32</v>
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="4"/>
     </row>
-    <row r="25">
+    <row r="25" spans="1:10" ht="12.75">
       <c r="A25" s="2"/>
       <c r="B25" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="11">
-        <v>4.0</v>
-      </c>
-      <c r="D25" s="11">
+        <v>30</v>
+      </c>
+      <c r="C25" s="2">
+        <v>4</v>
+      </c>
+      <c r="D25" s="2">
         <v>0.65</v>
       </c>
       <c r="E25" s="2">
         <f>E11</f>
-        <v>0.1</v>
-      </c>
-      <c r="F25" s="16"/>
-      <c r="G25" s="13">
+        <v>0.10</v>
+      </c>
+      <c r="F25" s="15"/>
+      <c r="G25" s="12">
         <f>PRODUCT(C25:E25)</f>
         <v>0.26</v>
       </c>
@@ -1175,57 +1288,57 @@
       <c r="I25" s="2"/>
       <c r="J25" s="4"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:10" ht="12.75">
       <c r="A26" s="2"/>
       <c r="B26" s="8" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C26" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D26" s="2">
-        <f t="shared" ref="D26:E26" si="3">D14</f>
-        <v>0.8</v>
+        <f>D14</f>
+        <v>0.80</v>
       </c>
       <c r="E26" s="2">
-        <f t="shared" si="3"/>
-        <v>0.8</v>
+        <f>E14</f>
+        <v>0.80</v>
       </c>
       <c r="F26" s="2"/>
-      <c r="G26" s="13">
-        <f t="shared" ref="G26:G27" si="4">PRODUCT(C26:F26)</f>
+      <c r="G26" s="12">
+        <f>PRODUCT(C26:F26)</f>
         <v>1.28</v>
       </c>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="4"/>
     </row>
-    <row r="27">
+    <row r="27" spans="1:10" ht="12.75">
       <c r="A27" s="2"/>
       <c r="B27" s="8" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C27" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D27" s="2">
         <f>D26</f>
-        <v>0.8</v>
+        <v>0.80</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2">
         <f>F14</f>
-        <v>0.1</v>
-      </c>
-      <c r="G27" s="13">
-        <f t="shared" si="4"/>
+        <v>0.10</v>
+      </c>
+      <c r="G27" s="12">
+        <f>PRODUCT(C27:F27)</f>
         <v>0.32</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="4"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:10" ht="12.75">
       <c r="A28" s="2"/>
       <c r="B28" s="8" t="s">
         <v>7</v>
@@ -1234,14 +1347,14 @@
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
-      <c r="G28" s="13">
+      <c r="G28" s="12">
         <f>SUM(G23:G27)</f>
         <v>4.68</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I28" s="11">
+        <v>26</v>
+      </c>
+      <c r="I28" s="2">
         <v>255.98</v>
       </c>
       <c r="J28" s="4">
@@ -1249,12 +1362,12 @@
         <v>1197.9864</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:10" ht="12.75">
       <c r="A29" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="B29" s="17" t="s">
-        <v>38</v>
+        <v>8</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
@@ -1263,14 +1376,14 @@
       <c r="G29" s="6"/>
       <c r="H29" s="6"/>
       <c r="I29" s="7"/>
-      <c r="J29" s="18">
+      <c r="J29" s="4">
         <v>101.29</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:10" ht="12.75">
       <c r="A30" s="2"/>
-      <c r="B30" s="19" t="s">
-        <v>39</v>
+      <c r="B30" s="16" t="s">
+        <v>34</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
@@ -1279,15 +1392,15 @@
       <c r="G30" s="6"/>
       <c r="H30" s="6"/>
       <c r="I30" s="7"/>
-      <c r="J30" s="20">
+      <c r="J30" s="17">
         <f>J5+J9+J12+J15+J18+J21+J28+J29</f>
-        <v>3800.002554</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="11"/>
-      <c r="B31" s="21" t="s">
-        <v>40</v>
+        <v>3800.0025540000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="12.75">
+      <c r="A31" s="2"/>
+      <c r="B31" s="18" t="s">
+        <v>35</v>
       </c>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
@@ -1312,12 +1425,6 @@
     <mergeCell ref="B16:J16"/>
     <mergeCell ref="B19:J19"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="landscape"/>
-  <headerFooter>
-    <oddFooter>&amp;RDirector            </oddFooter>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/GWD Data/Well Protection.xlsx
+++ b/GWD Data/Well Protection.xlsx
@@ -744,7 +744,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C74E1D98-5427-460A-B369-D3898F98B9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10AE242F-C717-4604-8A6F-4C92BBADB9A6}">
   <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/GWD Data/Well Protection.xlsx
+++ b/GWD Data/Well Protection.xlsx
@@ -744,7 +744,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10AE242F-C717-4604-8A6F-4C92BBADB9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDCBDBBE-AD8C-448A-9714-27117A62B9A6}">
   <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
